--- a/data/trans_orig/P1405-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P1405-Estudios-trans_orig.xlsx
@@ -536,7 +536,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de colitis en 2012</t>
+          <t>Población con diagnóstico de colitis en 2012 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>6277</t>
+          <t>5443</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21060</t>
+          <t>21057</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>23390</t>
+          <t>23030</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>45230</t>
+          <t>45075</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,75%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>32950</t>
+          <t>32403</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>61509</t>
+          <t>58713</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,54%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>953583</t>
+          <t>953586</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>968366</t>
+          <t>969200</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -864,7 +864,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,36%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1291384</t>
+          <t>1291539</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1313224</t>
+          <t>1313584</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,62%</t>
+          <t>96,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,25%</t>
+          <t>98,28%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2249748</t>
+          <t>2252544</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2278307</t>
+          <t>2278854</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,34%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,57%</t>
+          <t>98,6%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7304</t>
+          <t>7774</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25501</t>
+          <t>25409</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>13231</t>
+          <t>12359</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>32896</t>
+          <t>32120</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>24559</t>
+          <t>24578</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>51212</t>
+          <t>51519</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1164,7 +1164,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,39%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1938456</t>
+          <t>1938548</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1956653</t>
+          <t>1956183</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,7%</t>
+          <t>98,71%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,63%</t>
+          <t>99,6%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1721696</t>
+          <t>1722472</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1741361</t>
+          <t>1742233</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>98,17%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,25%</t>
+          <t>99,3%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3667337</t>
+          <t>3667030</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3693990</t>
+          <t>3693971</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,7 +1272,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,61%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>926</t>
+          <t>922</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7414</t>
+          <t>8113</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2840</t>
+          <t>2995</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15708</t>
+          <t>15596</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,43%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4604</t>
+          <t>4718</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>19901</t>
+          <t>18915</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1502,12 +1502,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,01%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>473767</t>
+          <t>473068</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>480255</t>
+          <t>480259</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,46%</t>
+          <t>98,31%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>442923</t>
+          <t>443035</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>455791</t>
+          <t>455636</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,6%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,38%</t>
+          <t>99,35%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>919912</t>
+          <t>920898</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>935209</t>
+          <t>935095</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,12 +1615,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,88%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,5%</t>
         </is>
       </c>
     </row>
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>18935</t>
+          <t>19243</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>42033</t>
+          <t>41702</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,56%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>47226</t>
+          <t>46026</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>81312</t>
+          <t>78895</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,12 +1810,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1830,12 +1830,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>71643</t>
+          <t>71629</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>112531</t>
+          <t>111915</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3377749</t>
+          <t>3378080</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3400847</t>
+          <t>3400539</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,77%</t>
+          <t>98,78%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,45%</t>
+          <t>99,44%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3468525</t>
+          <t>3470942</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3502611</t>
+          <t>3503811</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,12 +1923,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,71%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,7%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1943,12 +1943,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6857088</t>
+          <t>6857704</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6897976</t>
+          <t>6897990</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -2139,7 +2139,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con diagnóstico de colitis en 2016</t>
+          <t>Población con diagnóstico de colitis en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2339,7 +2339,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8244</t>
+          <t>8280</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2354,7 +2354,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2369,12 +2369,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>17150</t>
+          <t>16752</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>39679</t>
+          <t>38221</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2384,12 +2384,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,99%</t>
+          <t>3,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2404,12 +2404,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18846</t>
+          <t>18147</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>41543</t>
+          <t>41120</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2419,12 +2419,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,38%</t>
+          <t>2,35%</t>
         </is>
       </c>
     </row>
@@ -2447,7 +2447,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>746103</t>
+          <t>746067</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -2462,7 +2462,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>954981</t>
+          <t>956439</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>977510</t>
+          <t>977908</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,01%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,32%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1707464</t>
+          <t>1707887</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1730161</t>
+          <t>1730860</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,62%</t>
+          <t>97,65%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,96%</t>
         </is>
       </c>
     </row>
@@ -2677,12 +2677,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10170</t>
+          <t>10381</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>27645</t>
+          <t>28633</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2692,12 +2692,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2712,12 +2712,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>18345</t>
+          <t>17953</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>39647</t>
+          <t>38850</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2727,12 +2727,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2747,12 +2747,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>31726</t>
+          <t>31630</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>58516</t>
+          <t>59208</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2767,7 +2767,7 @@
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,46%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2048740</t>
+          <t>2047752</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2066215</t>
+          <t>2066004</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,67%</t>
+          <t>98,62%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,51%</t>
+          <t>99,5%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1948653</t>
+          <t>1949450</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1969955</t>
+          <t>1970347</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,01%</t>
+          <t>98,05%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,1%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4006169</t>
+          <t>4005477</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4032959</t>
+          <t>4033055</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2875,7 +2875,7 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,54%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1011</t>
+          <t>1013</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12051</t>
+          <t>12772</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3035,12 +3035,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,19%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1026</t>
+          <t>1024</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8700</t>
+          <t>8831</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,61%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2930</t>
+          <t>2823</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16813</t>
+          <t>16555</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3105,12 +3105,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,27%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,53%</t>
+          <t>1,51%</t>
         </is>
       </c>
     </row>
@@ -3133,12 +3133,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>534835</t>
+          <t>534114</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>545875</t>
+          <t>545873</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3148,12 +3148,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,8%</t>
+          <t>97,66%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>99,82%</t>
+          <t>99,81%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>540440</t>
+          <t>540309</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>548114</t>
+          <t>548116</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3183,7 +3183,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,42%</t>
+          <t>98,39%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1079214</t>
+          <t>1079472</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1093097</t>
+          <t>1093204</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3218,12 +3218,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,73%</t>
+          <t>99,74%</t>
         </is>
       </c>
     </row>
@@ -3363,12 +3363,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>15190</t>
+          <t>14583</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>36873</t>
+          <t>36394</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3378,12 +3378,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3398,12 +3398,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>40158</t>
+          <t>41816</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>71241</t>
+          <t>72307</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3413,12 +3413,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3433,12 +3433,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>63265</t>
+          <t>62874</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>101577</t>
+          <t>99774</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3448,12 +3448,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,47%</t>
+          <t>1,44%</t>
         </is>
       </c>
     </row>
@@ -3476,12 +3476,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3340745</t>
+          <t>3341224</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3362428</t>
+          <t>3363035</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3491,12 +3491,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,91%</t>
+          <t>98,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,55%</t>
+          <t>99,57%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3460859</t>
+          <t>3459793</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3491942</t>
+          <t>3490284</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3526,12 +3526,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,98%</t>
+          <t>97,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,86%</t>
+          <t>98,82%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6808141</t>
+          <t>6809944</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6846453</t>
+          <t>6846844</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3561,12 +3561,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,53%</t>
+          <t>98,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,08%</t>
+          <t>99,09%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P1405-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P1405-Estudios-trans_orig.xlsx
@@ -731,12 +731,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5443</t>
+          <t>6193</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>21057</t>
+          <t>21323</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -746,12 +746,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -766,12 +766,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>23030</t>
+          <t>23100</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>45075</t>
+          <t>46408</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -781,12 +781,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>1,73%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -801,12 +801,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>32403</t>
+          <t>32887</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>58713</t>
+          <t>58873</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -816,12 +816,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,55%</t>
         </is>
       </c>
     </row>
@@ -844,12 +844,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>953586</t>
+          <t>953320</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>969200</t>
+          <t>968450</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -859,12 +859,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>97,84%</t>
+          <t>97,81%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,36%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -879,12 +879,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1291539</t>
+          <t>1290206</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>1313584</t>
+          <t>1313514</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -894,12 +894,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,63%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,28%</t>
+          <t>98,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -914,12 +914,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>2252544</t>
+          <t>2252384</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>2278854</t>
+          <t>2278370</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -929,12 +929,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,46%</t>
+          <t>97,45%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>98,6%</t>
+          <t>98,58%</t>
         </is>
       </c>
     </row>
@@ -1074,12 +1074,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>7774</t>
+          <t>8098</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>25409</t>
+          <t>26618</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1089,12 +1089,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,41%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,36%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1109,12 +1109,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>12359</t>
+          <t>12975</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>32120</t>
+          <t>33314</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1124,12 +1124,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1144,12 +1144,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>24578</t>
+          <t>23414</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>51519</t>
+          <t>50029</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,66%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,39%</t>
+          <t>1,35%</t>
         </is>
       </c>
     </row>
@@ -1187,12 +1187,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1938548</t>
+          <t>1937339</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>1956183</t>
+          <t>1955859</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1202,12 +1202,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,71%</t>
+          <t>98,64%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,6%</t>
+          <t>99,59%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1222,12 +1222,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1722472</t>
+          <t>1721278</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1742233</t>
+          <t>1741617</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,17%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>99,3%</t>
+          <t>99,26%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1257,12 +1257,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3667030</t>
+          <t>3668520</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>3693971</t>
+          <t>3695135</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1272,12 +1272,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,61%</t>
+          <t>98,65%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,34%</t>
+          <t>99,37%</t>
         </is>
       </c>
     </row>
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>922</t>
+          <t>910</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>8113</t>
+          <t>7845</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1437,7 +1437,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1452,12 +1452,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>2995</t>
+          <t>2789</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>15596</t>
+          <t>15269</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1487,12 +1487,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>4718</t>
+          <t>4721</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>18915</t>
+          <t>19986</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1507,7 +1507,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>2,13%</t>
         </is>
       </c>
     </row>
@@ -1530,12 +1530,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>473068</t>
+          <t>473336</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>480259</t>
+          <t>480271</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1545,7 +1545,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>98,31%</t>
+          <t>98,37%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1565,12 +1565,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>443035</t>
+          <t>443362</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>455636</t>
+          <t>455842</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1580,12 +1580,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>96,6%</t>
+          <t>96,67%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>99,35%</t>
+          <t>99,39%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1600,12 +1600,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>920898</t>
+          <t>919827</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>935095</t>
+          <t>935092</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1615,7 +1615,7 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>97,99%</t>
+          <t>97,87%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
@@ -1760,12 +1760,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>19243</t>
+          <t>18569</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>41702</t>
+          <t>42096</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1775,12 +1775,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,56%</t>
+          <t>0,54%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1795,12 +1795,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>46026</t>
+          <t>47561</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>78895</t>
+          <t>81017</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1810,42 +1810,42 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
+          <t>1,34%</t>
+        </is>
+      </c>
+      <c r="P13" s="2" t="inlineStr">
+        <is>
+          <t>2,28%</t>
+        </is>
+      </c>
+      <c r="Q13" s="2" t="inlineStr">
+        <is>
+          <t>80</t>
+        </is>
+      </c>
+      <c r="R13" s="2" t="inlineStr">
+        <is>
+          <t>90386</t>
+        </is>
+      </c>
+      <c r="S13" s="2" t="inlineStr">
+        <is>
+          <t>71108</t>
+        </is>
+      </c>
+      <c r="T13" s="2" t="inlineStr">
+        <is>
+          <t>112449</t>
+        </is>
+      </c>
+      <c r="U13" s="2" t="inlineStr">
+        <is>
           <t>1,3%</t>
         </is>
       </c>
-      <c r="P13" s="2" t="inlineStr">
-        <is>
-          <t>2,22%</t>
-        </is>
-      </c>
-      <c r="Q13" s="2" t="inlineStr">
-        <is>
-          <t>80</t>
-        </is>
-      </c>
-      <c r="R13" s="2" t="inlineStr">
-        <is>
-          <t>90386</t>
-        </is>
-      </c>
-      <c r="S13" s="2" t="inlineStr">
-        <is>
-          <t>71629</t>
-        </is>
-      </c>
-      <c r="T13" s="2" t="inlineStr">
-        <is>
-          <t>111915</t>
-        </is>
-      </c>
-      <c r="U13" s="2" t="inlineStr">
-        <is>
-          <t>1,3%</t>
-        </is>
-      </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,02%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
@@ -1873,12 +1873,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3378080</t>
+          <t>3377686</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3400539</t>
+          <t>3401213</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1888,12 +1888,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,78%</t>
+          <t>98,77%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,44%</t>
+          <t>99,46%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1908,12 +1908,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3470942</t>
+          <t>3468820</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3503811</t>
+          <t>3502276</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1923,39 +1923,39 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,72%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
+          <t>98,66%</t>
+        </is>
+      </c>
+      <c r="Q14" s="2" t="inlineStr">
+        <is>
+          <t>6413</t>
+        </is>
+      </c>
+      <c r="R14" s="2" t="inlineStr">
+        <is>
+          <t>6879233</t>
+        </is>
+      </c>
+      <c r="S14" s="2" t="inlineStr">
+        <is>
+          <t>6857170</t>
+        </is>
+      </c>
+      <c r="T14" s="2" t="inlineStr">
+        <is>
+          <t>6898511</t>
+        </is>
+      </c>
+      <c r="U14" s="2" t="inlineStr">
+        <is>
           <t>98,7%</t>
         </is>
       </c>
-      <c r="Q14" s="2" t="inlineStr">
-        <is>
-          <t>6413</t>
-        </is>
-      </c>
-      <c r="R14" s="2" t="inlineStr">
-        <is>
-          <t>6879233</t>
-        </is>
-      </c>
-      <c r="S14" s="2" t="inlineStr">
-        <is>
-          <t>6857704</t>
-        </is>
-      </c>
-      <c r="T14" s="2" t="inlineStr">
-        <is>
-          <t>6897990</t>
-        </is>
-      </c>
-      <c r="U14" s="2" t="inlineStr">
-        <is>
-          <t>98,7%</t>
-        </is>
-      </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
           <t>98,39%</t>
@@ -1963,7 +1963,7 @@
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,97%</t>
+          <t>98,98%</t>
         </is>
       </c>
     </row>
@@ -2339,7 +2339,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>8280</t>
+          <t>7532</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2354,7 +2354,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2369,12 +2369,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>16752</t>
+          <t>16541</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>38221</t>
+          <t>37803</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2384,12 +2384,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,66%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,8%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2404,12 +2404,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>18147</t>
+          <t>18126</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>41120</t>
+          <t>41506</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2424,7 +2424,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,37%</t>
         </is>
       </c>
     </row>
@@ -2447,7 +2447,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>746067</t>
+          <t>746815</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -2462,7 +2462,7 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>98,9%</t>
+          <t>99,0%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>956439</t>
+          <t>956857</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>977908</t>
+          <t>978119</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>96,16%</t>
+          <t>96,2%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>98,32%</t>
+          <t>98,34%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1707887</t>
+          <t>1707501</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>1730860</t>
+          <t>1730881</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2532,7 +2532,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>97,65%</t>
+          <t>97,63%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -2677,12 +2677,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10381</t>
+          <t>10090</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>28633</t>
+          <t>27553</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2692,12 +2692,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,49%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2712,12 +2712,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>17953</t>
+          <t>17850</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>38850</t>
+          <t>37788</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2732,7 +2732,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>1,95%</t>
+          <t>1,9%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2747,12 +2747,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>31630</t>
+          <t>32160</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>59208</t>
+          <t>59920</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2762,12 +2762,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>1,46%</t>
+          <t>1,47%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2047752</t>
+          <t>2048832</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>2066004</t>
+          <t>2066295</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>98,62%</t>
+          <t>98,67%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>99,5%</t>
+          <t>99,51%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1949450</t>
+          <t>1950512</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>1970347</t>
+          <t>1970450</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2840,7 +2840,7 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>98,05%</t>
+          <t>98,1%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4005477</t>
+          <t>4004765</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>4033055</t>
+          <t>4032525</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>98,54%</t>
+          <t>98,53%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>99,22%</t>
+          <t>99,21%</t>
         </is>
       </c>
     </row>
@@ -3020,12 +3020,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1013</t>
+          <t>1021</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>12772</t>
+          <t>12663</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3040,7 +3040,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,32%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>1024</t>
+          <t>1023</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>8831</t>
+          <t>8568</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,56%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>2823</t>
+          <t>3095</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>16555</t>
+          <t>16942</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3105,12 +3105,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,28%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,51%</t>
+          <t>1,55%</t>
         </is>
       </c>
     </row>
@@ -3133,12 +3133,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>534114</t>
+          <t>534223</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>545873</t>
+          <t>545865</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3148,7 +3148,7 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>97,66%</t>
+          <t>97,68%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>540309</t>
+          <t>540572</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>548116</t>
+          <t>548117</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3183,7 +3183,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>98,39%</t>
+          <t>98,44%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1079472</t>
+          <t>1079085</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1093204</t>
+          <t>1092932</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3218,12 +3218,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>98,49%</t>
+          <t>98,45%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>99,74%</t>
+          <t>99,72%</t>
         </is>
       </c>
     </row>
@@ -3363,12 +3363,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>14583</t>
+          <t>15276</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>36394</t>
+          <t>37217</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3378,12 +3378,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,45%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3398,12 +3398,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>41816</t>
+          <t>42091</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>72307</t>
+          <t>71347</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3413,12 +3413,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,18%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3433,12 +3433,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>62874</t>
+          <t>63443</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>99774</t>
+          <t>100382</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3448,12 +3448,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,45%</t>
         </is>
       </c>
     </row>
@@ -3476,12 +3476,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>3341224</t>
+          <t>3340401</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>3363035</t>
+          <t>3362342</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3491,12 +3491,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>98,92%</t>
+          <t>98,9%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>99,57%</t>
+          <t>99,55%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3511,12 +3511,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>3459793</t>
+          <t>3460753</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>3490284</t>
+          <t>3490009</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3526,12 +3526,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>97,95%</t>
+          <t>97,98%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,82%</t>
+          <t>98,81%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3546,12 +3546,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>6809944</t>
+          <t>6809336</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>6846844</t>
+          <t>6846275</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3561,12 +3561,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>98,56%</t>
+          <t>98,55%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>99,09%</t>
+          <t>99,08%</t>
         </is>
       </c>
     </row>
